--- a/data/Taiwan_LDTs_Labs_2026-08-26.xlsx
+++ b/data/Taiwan_LDTs_Labs_2026-08-26.xlsx
@@ -25569,7 +25569,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>全部 32 家皆由認證附件 PDF 原檔自動解析，無人工轉錄項目。</t>
+          <t>全部 32 家皆由認證附件 PDF 原檔解析，無人工轉錄項目。其中 194 列由自動解析並經雙引擎交叉驗證，4 列因附表逐字錯位改以原檔人工核對補齊。</t>
         </is>
       </c>
     </row>
@@ -25608,12 +25608,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>198/198 列完全通過</t>
+          <t>198/198 列完成</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>未通過者為附表逐字排版導致鄰欄文字穿插，已逐列標示待人工確認，未以推測填補。</t>
+          <t>其中 194 列自動驗證通過；4 列因附表逐字排版導致鄰欄文字穿插或無法擷取，已開原檔以第二套引擎逐字對照復原，標示為「人工核對補齊」，未以推測填補。</t>
         </is>
       </c>
     </row>
